--- a/scripts/student-imports/transfers/inputs/student-transfer.xlsx
+++ b/scripts/student-imports/transfers/inputs/student-transfer.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\edu-affairs-v2\scripts\student-imports\transfers\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5CEF63-F8AA-4ECA-883A-A26D2DC12F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{892F5134-4011-4D76-B43E-8D599378D420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5790" yWindow="2475" windowWidth="19905" windowHeight="10605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="2370" windowWidth="15705" windowHeight="11655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="students" sheetId="1" r:id="rId1"/>
+    <sheet name="students (2)" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="45">
   <si>
     <t>studentId</t>
   </si>
@@ -131,13 +132,37 @@
   </si>
   <si>
     <t>1205591645</t>
+  </si>
+  <si>
+    <t>دانة محمد عبدالعزيز الفراج</t>
+  </si>
+  <si>
+    <t>student-1788968763108</t>
+  </si>
+  <si>
+    <t>TRANSFER</t>
+  </si>
+  <si>
+    <t>ليان عبدالمجيد غنام الغنام</t>
+  </si>
+  <si>
+    <t>من الروضة الاولى الى الثالثة النجوم</t>
+  </si>
+  <si>
+    <t>student-1788956670839</t>
+  </si>
+  <si>
+    <t>1202539456</t>
+  </si>
+  <si>
+    <t>kg-03</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -185,8 +210,16 @@
       <color rgb="FF682B45"/>
       <name val="Tajawal"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Tajawal"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -196,6 +229,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -218,7 +257,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -253,6 +292,17 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -465,6 +515,79 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="15.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="33">
+      <c r="A2" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="11" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17071649-D7EB-4558-BD46-350E3F6D5BF4}">
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -577,7 +700,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="33">
+    <row r="5" spans="1:8" ht="16.5">
       <c r="A5" s="7" t="s">
         <v>23</v>
       </c>
@@ -603,7 +726,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="33">
+    <row r="6" spans="1:8" ht="16.5">
       <c r="A6" s="7" t="s">
         <v>26</v>
       </c>
@@ -629,7 +752,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="33">
+    <row r="7" spans="1:8" ht="16.5">
       <c r="A7" s="7" t="s">
         <v>29</v>
       </c>
@@ -655,10 +778,16 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" ht="33">
+      <c r="A8" s="13" t="s">
+        <v>38</v>
+      </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="F8" s="4"/>
+      <c r="G8" s="12" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="9" spans="1:8">
       <c r="C9" s="4"/>

--- a/scripts/student-imports/transfers/inputs/student-transfer.xlsx
+++ b/scripts/student-imports/transfers/inputs/student-transfer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\edu-affairs-v2\scripts\student-imports\transfers\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{892F5134-4011-4D76-B43E-8D599378D420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91DDD2C5-D272-4392-A30C-79E69509DEB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="2370" windowWidth="15705" windowHeight="11655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="students" sheetId="1" r:id="rId1"/>
@@ -143,19 +143,19 @@
     <t>TRANSFER</t>
   </si>
   <si>
-    <t>ليان عبدالمجيد غنام الغنام</t>
-  </si>
-  <si>
-    <t>من الروضة الاولى الى الثالثة النجوم</t>
-  </si>
-  <si>
-    <t>student-1788956670839</t>
-  </si>
-  <si>
-    <t>1202539456</t>
-  </si>
-  <si>
-    <t>kg-03</t>
+    <t>kg-04</t>
+  </si>
+  <si>
+    <t>نجيبه من الحضور والغياب من عند الوكيلة مثلا، ثم تدخل على فصل الطالب بتلاقيه</t>
+  </si>
+  <si>
+    <t>بدر محمدعبدالله الحمين</t>
+  </si>
+  <si>
+    <t>student-1788959725293</t>
+  </si>
+  <si>
+    <t>1200748166</t>
   </si>
 </sst>
 </file>
@@ -219,7 +219,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -229,12 +229,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -257,7 +251,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -298,10 +292,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -515,21 +506,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="15.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.75" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.5" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.75" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.5" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15">
+    <row r="1" spans="1:7" ht="15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -549,36 +540,28 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="33">
-      <c r="A2" s="13" t="s">
-        <v>42</v>
+    <row r="2" spans="1:7" ht="15.75">
+      <c r="A2" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="15" t="s">
         <v>15</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="F3" s="4"/>
+      <c r="G2" t="s">
+        <v>42</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
@@ -790,6 +773,9 @@
       </c>
     </row>
     <row r="9" spans="1:8">
+      <c r="A9" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="F9" s="4"/>

--- a/scripts/student-imports/transfers/inputs/student-transfer.xlsx
+++ b/scripts/student-imports/transfers/inputs/student-transfer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\edu-affairs-v2\scripts\student-imports\transfers\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91DDD2C5-D272-4392-A30C-79E69509DEB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0FB7750-92D4-4389-B4FD-83C03A389F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9540" yWindow="3255" windowWidth="15705" windowHeight="11655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="students" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="45">
   <si>
     <t>studentId</t>
   </si>
@@ -143,26 +143,26 @@
     <t>TRANSFER</t>
   </si>
   <si>
-    <t>kg-04</t>
-  </si>
-  <si>
     <t>نجيبه من الحضور والغياب من عند الوكيلة مثلا، ثم تدخل على فصل الطالب بتلاقيه</t>
   </si>
   <si>
-    <t>بدر محمدعبدالله الحمين</t>
-  </si>
-  <si>
-    <t>student-1788959725293</t>
-  </si>
-  <si>
-    <t>1200748166</t>
+    <t>student-1787856664437</t>
+  </si>
+  <si>
+    <t>mrb-girls</t>
+  </si>
+  <si>
+    <t>ليما بدر علي الشايع</t>
+  </si>
+  <si>
+    <t>g3-general-1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -217,6 +217,16 @@
     <font>
       <sz val="8"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Tajawal"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -251,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -292,8 +302,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -510,7 +523,7 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" style="2" customWidth="1"/>
     <col min="3" max="3" width="14" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.5" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.625" style="2" bestFit="1" customWidth="1"/>
@@ -540,27 +553,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75">
+    <row r="2" spans="1:7" ht="16.5">
       <c r="A2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="B2" s="15">
+        <v>1185085840</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="15" t="s">
-        <v>15</v>
+      <c r="E2" s="16" t="s">
+        <v>44</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G2" t="s">
-        <v>42</v>
+      <c r="G2" s="14" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -774,7 +787,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>

--- a/scripts/student-imports/transfers/inputs/student-transfer.xlsx
+++ b/scripts/student-imports/transfers/inputs/student-transfer.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\edu-affairs-v2\scripts\student-imports\transfers\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0FB7750-92D4-4389-B4FD-83C03A389F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA426BFA-B06B-4200-A3BB-CFD6F870E0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9540" yWindow="3255" windowWidth="15705" windowHeight="11655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="105" yWindow="6255" windowWidth="14325" windowHeight="7485" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="students" sheetId="1" r:id="rId1"/>
     <sheet name="students (2)" sheetId="2" r:id="rId2"/>
+    <sheet name="students (3)" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="53">
   <si>
     <t>studentId</t>
   </si>
@@ -143,26 +144,50 @@
     <t>TRANSFER</t>
   </si>
   <si>
-    <t>نجيبه من الحضور والغياب من عند الوكيلة مثلا، ثم تدخل على فصل الطالب بتلاقيه</t>
-  </si>
-  <si>
-    <t>student-1787856664437</t>
-  </si>
-  <si>
-    <t>mrb-girls</t>
-  </si>
-  <si>
-    <t>ليما بدر علي الشايع</t>
-  </si>
-  <si>
-    <t>g3-general-1</t>
+    <t>دانة الفراج الاوركيد</t>
+  </si>
+  <si>
+    <t>سلاف الدهام التوليب</t>
+  </si>
+  <si>
+    <t>احمد الباتل الكادي</t>
+  </si>
+  <si>
+    <t>دان الحمدان الكادي</t>
+  </si>
+  <si>
+    <t>kg-02</t>
+  </si>
+  <si>
+    <t>kg1-a</t>
+  </si>
+  <si>
+    <t>نجيبه من الفصول من عند الوكيلة مثلا، ثم تدخل على فصل الطالب بتلاقيه</t>
+  </si>
+  <si>
+    <t>1203631591</t>
+  </si>
+  <si>
+    <t>1201344031</t>
+  </si>
+  <si>
+    <t>بدر محمدعبدالله الحمين</t>
+  </si>
+  <si>
+    <t>1200748166</t>
+  </si>
+  <si>
+    <t>kg-04</t>
+  </si>
+  <si>
+    <t>student-1790604863204</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -220,13 +245,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Tajawal"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Google Sans"/>
     </font>
   </fonts>
   <fills count="3">
@@ -302,11 +321,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -519,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20.75" style="2" bestFit="1" customWidth="1"/>
@@ -553,32 +570,43 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="16.5">
-      <c r="A2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="15">
-        <v>1185085840</v>
+    <row r="2" spans="1:7" ht="15.75">
+      <c r="A2" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>31</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="14" t="s">
-        <v>43</v>
-      </c>
+      <c r="G2" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="F6" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -787,7 +815,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -806,4 +834,148 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B90BA01-47ED-4B0A-B9CF-7F6C6EF2374C}">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="20.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="B2" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="B3" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="B4" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="D6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="D7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="C9" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="C10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/scripts/student-imports/transfers/inputs/student-transfer.xlsx
+++ b/scripts/student-imports/transfers/inputs/student-transfer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\edu-affairs-v2\scripts\student-imports\transfers\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA426BFA-B06B-4200-A3BB-CFD6F870E0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C03F47C7-4F27-4F85-9C08-6C50AC3483D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="105" yWindow="6255" windowWidth="14325" windowHeight="7485" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6915" yWindow="4425" windowWidth="17115" windowHeight="7485" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="students" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="54">
   <si>
     <t>studentId</t>
   </si>
@@ -180,14 +180,17 @@
     <t>kg-04</t>
   </si>
   <si>
-    <t>student-1790604863204</t>
+    <t>student-1788956694131</t>
+  </si>
+  <si>
+    <t>1200654935</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -242,10 +245,6 @@
     <font>
       <sz val="8"/>
       <name val="Carlito"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Google Sans"/>
     </font>
   </fonts>
   <fills count="3">
@@ -323,7 +322,7 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -536,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20.75" style="2" bestFit="1" customWidth="1"/>
@@ -550,7 +549,7 @@
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15">
+    <row r="1" spans="1:6" ht="15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -570,15 +569,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75">
+    <row r="2" spans="1:6" ht="15.75">
       <c r="A2" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>50</v>
+      <c r="B2" s="14" t="s">
+        <v>53</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>7</v>
@@ -589,19 +588,16 @@
       <c r="F2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="F6" s="4"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="F4" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
